--- a/progress.xlsx
+++ b/progress.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0879F7A-65E6-4C1A-873E-3D0231023512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C4D910-D20A-4A3B-8880-44715329EB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="19">
   <si>
     <t>Task</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Inspection</t>
-  </si>
-  <si>
-    <t>Delay</t>
   </si>
   <si>
     <t>Weather</t>
@@ -447,7 +444,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -458,7 +455,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1">
         <v>46130</v>
@@ -469,7 +466,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1">
         <v>46131</v>
@@ -480,7 +477,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1">
         <v>46132</v>
@@ -491,7 +488,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
         <v>46133</v>
@@ -502,7 +499,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <v>46134</v>
@@ -513,49 +510,49 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1">
         <v>46135</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1">
         <v>46136</v>
       </c>
       <c r="C8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1">
         <v>46137</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1">
         <v>46138</v>
@@ -566,7 +563,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
         <v>46139</v>
@@ -577,7 +574,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1">
         <v>46140</v>
@@ -588,7 +585,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="1">
         <v>46141</v>
@@ -599,35 +596,35 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1">
         <v>46142</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="1">
         <v>46143</v>
       </c>
       <c r="C15" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1">
         <v>46144</v>
@@ -638,7 +635,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="1">
         <v>46145</v>
@@ -649,21 +646,21 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1">
         <v>46146</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" s="1">
         <v>46147</v>
@@ -674,7 +671,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="1">
         <v>46148</v>
@@ -685,63 +682,63 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1">
         <v>46149</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1">
         <v>46150</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1">
         <v>46151</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1">
         <v>46152</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1">
         <v>46153</v>
@@ -752,7 +749,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" s="1">
         <v>46154</v>
@@ -763,7 +760,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1">
         <v>46155</v>
@@ -774,7 +771,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28" s="1">
         <v>46156</v>
@@ -785,7 +782,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29" s="1">
         <v>46157</v>
@@ -796,35 +793,35 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="1">
         <v>46158</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B31" s="1">
         <v>46159</v>
       </c>
       <c r="C31" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B32" s="1">
         <v>46160</v>
@@ -835,7 +832,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B33" s="1">
         <v>46161</v>
@@ -846,7 +843,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B34" s="1">
         <v>46162</v>
@@ -857,7 +854,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B35" s="1">
         <v>46163</v>
@@ -868,7 +865,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B36" s="1">
         <v>46164</v>
@@ -879,7 +876,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B37" s="1">
         <v>46165</v>
@@ -890,7 +887,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B38" s="1">
         <v>46166</v>
@@ -901,7 +898,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B39" s="1">
         <v>46167</v>
@@ -912,91 +909,91 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" s="1">
         <v>46168</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41" s="1">
         <v>46169</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42" s="1">
         <v>46170</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B43" s="1">
         <v>46171</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B44" s="1">
         <v>46172</v>
       </c>
       <c r="C44" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B45" s="1">
         <v>46173</v>
       </c>
       <c r="C45" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" s="1">
         <v>46174</v>
@@ -1007,7 +1004,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B47" s="1">
         <v>46175</v>
@@ -1018,7 +1015,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B48" s="1">
         <v>46176</v>
@@ -1029,7 +1026,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B49" s="1">
         <v>46177</v>
@@ -1040,7 +1037,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B50" s="1">
         <v>46178</v>
@@ -1051,35 +1048,35 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B51" s="1">
         <v>46179</v>
       </c>
       <c r="C51" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D51" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B52" s="1">
         <v>46180</v>
       </c>
       <c r="C52" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D52" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B53" s="1">
         <v>46181</v>
@@ -1090,16 +1087,16 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B54" s="1">
         <v>46182</v>
       </c>
       <c r="C54" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D6882D-9358-4044-A7B9-FB6F3B9074FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7D9924-5DBA-4E48-B9EB-F1EA6A5A6348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="43">
   <si>
     <t>Task</t>
   </si>
@@ -196,6 +196,9 @@
   <si>
     <t>nan</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegB (Re-do scour)</t>
   </si>
 </sst>
 </file>
@@ -1626,7 +1629,9 @@
       <c r="H38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I38" s="2"/>
+      <c r="I38" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7D9924-5DBA-4E48-B9EB-F1EA6A5A6348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070BAA2A-5BC0-48D9-962A-3D13BB59928D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="44">
   <si>
     <t>Task</t>
   </si>
@@ -199,6 +199,10 @@
   </si>
   <si>
     <t>LegB (Re-do scour)</t>
+  </si>
+  <si>
+    <t>OCC canceled today's mission due to high wave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1319,7 +1323,7 @@
         <v>46156</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>19</v>
@@ -1397,7 +1401,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="3">
@@ -1411,7 +1415,7 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -1646,7 +1650,7 @@
         <v>46167</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>19</v>
@@ -1866,7 +1870,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B48" s="2">
         <v>1</v>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207905B0-F826-4DA4-A5B6-F57283910BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA64FAD-11EC-417A-B565-B0AE4C24D26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="48">
   <si>
     <t>Task</t>
   </si>
@@ -215,6 +215,10 @@
   </si>
   <si>
     <t>Category</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Progress</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -222,7 +226,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,13 +241,49 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -255,10 +295,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -269,9 +313,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{82E2E59F-3CB1-4560-A332-AE3CB4876186}"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -549,1740 +610,1906 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" customWidth="1"/>
-    <col min="5" max="5" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="137.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.09765625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.59765625" customWidth="1"/>
+    <col min="6" max="6" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.09765625" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="137.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="5">
+        <v>0.60980000000000001</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="2">
         <v>46130</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>2</v>
+      <c r="E2" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="1"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="6">
+        <v>0.75609756097560976</v>
+      </c>
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
         <v>46131</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>2</v>
+      <c r="E3" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="6">
+        <v>0.85365853658536583</v>
+      </c>
+      <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
         <v>46132</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>2</v>
+      <c r="E4" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
         <v>46133</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>2</v>
+      <c r="E5" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="7">
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
         <v>46134</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>2</v>
+      <c r="E6" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="2">
+      <c r="B7" s="5">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="2">
         <v>46135</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="1"/>
+      <c r="K7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2">
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="2">
         <v>46136</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="2">
+      <c r="B9" s="5">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="2">
         <v>46137</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="7">
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="C10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" s="2">
+      <c r="D10" s="2">
         <v>46138</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>2</v>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="7">
+        <v>0.72972972972972971</v>
+      </c>
+      <c r="C11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="2">
+      <c r="D11" s="2">
         <v>46139</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>2</v>
+      <c r="E11" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="7">
+        <v>0.89189189189189189</v>
+      </c>
+      <c r="C12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="2">
+      <c r="D12" s="2">
         <v>46140</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>2</v>
+      <c r="E12" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="7">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="C13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="2">
+      <c r="D13" s="2">
         <v>46141</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>2</v>
+      <c r="E13" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="1"/>
+      <c r="K13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="2">
+      <c r="B14" s="5">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="2">
         <v>46142</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="1"/>
+      <c r="K14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="2">
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="2">
         <v>46143</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15" s="1"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="7">
+        <v>0.29729729729729731</v>
+      </c>
+      <c r="C16" s="1">
         <v>5</v>
       </c>
-      <c r="C16" s="2">
+      <c r="D16" s="2">
         <v>46144</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>2</v>
+      <c r="E16" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16" s="1"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="7">
+        <v>0.51351351351351349</v>
+      </c>
+      <c r="C17" s="1">
         <v>5</v>
       </c>
-      <c r="C17" s="2">
+      <c r="D17" s="2">
         <v>46145</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>2</v>
+      <c r="E17" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="1"/>
+      <c r="K17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17" s="1"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="2">
+      <c r="B18" s="5">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="2">
         <v>46146</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="1"/>
+      <c r="H18" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="I18" s="1"/>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="1"/>
+      <c r="K18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="7">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1">
         <v>5</v>
       </c>
-      <c r="C19" s="2">
+      <c r="D19" s="2">
         <v>46147</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>2</v>
+      <c r="E19" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19" s="1"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="7">
+        <v>0.16216216216216217</v>
+      </c>
+      <c r="C20" s="1">
         <v>5</v>
       </c>
-      <c r="C20" s="2">
+      <c r="D20" s="2">
         <v>46148</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>2</v>
+      <c r="E20" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20" s="1"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="2">
+      <c r="B21" s="5">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="2">
         <v>46149</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="1"/>
+      <c r="K21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O21" s="1"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="2">
+      <c r="B22" s="5">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="2">
         <v>46150</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="1" t="s">
+      <c r="J22" s="1"/>
+      <c r="K22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O22" s="1"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="2">
+      <c r="B23" s="5">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="2">
         <v>46151</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="1" t="s">
+      <c r="J23" s="1"/>
+      <c r="K23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O23" s="1"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="2">
+      <c r="B24" s="5">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="2">
         <v>46152</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="1"/>
+      <c r="K24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="1">
-        <v>4</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="B25" s="7">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2">
         <v>46153</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>2</v>
+      <c r="E25" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="1">
-        <v>4</v>
-      </c>
-      <c r="C26" s="2">
+      <c r="B26" s="7">
+        <v>0.59459459459459463</v>
+      </c>
+      <c r="C26" s="1">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2">
         <v>46154</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>2</v>
+      <c r="E26" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="1">
-        <v>4</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B27" s="7">
+        <v>0.67567567567567566</v>
+      </c>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2">
         <v>46155</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>2</v>
+      <c r="E27" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="1">
-        <v>4</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" s="7">
+        <v>0.67567567567567566</v>
+      </c>
+      <c r="C28" s="1">
+        <v>4</v>
+      </c>
+      <c r="D28" s="2">
         <v>46156</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>4</v>
+      <c r="E28" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="1">
-        <v>4</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="7">
+        <v>0.89189189189189189</v>
+      </c>
+      <c r="C29" s="1">
+        <v>4</v>
+      </c>
+      <c r="D29" s="2">
         <v>46157</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>2</v>
+      <c r="E29" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="2">
+      <c r="B30" s="5">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="2">
         <v>46158</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
+      <c r="J30" s="1"/>
+      <c r="K30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="1">
-        <v>4</v>
-      </c>
-      <c r="C31" s="2">
+      <c r="B31" s="7">
+        <v>0.89189189189189189</v>
+      </c>
+      <c r="C31" s="1">
+        <v>4</v>
+      </c>
+      <c r="D31" s="2">
         <v>46159</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F31" s="1"/>
+      <c r="E31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="1" t="s">
+      <c r="J31" s="1"/>
+      <c r="K31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1">
-        <v>3</v>
-      </c>
-      <c r="C32" s="2">
+        <v>38</v>
+      </c>
+      <c r="B32" s="7">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1">
+        <v>4</v>
+      </c>
+      <c r="D32" s="2">
         <v>46160</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>2</v>
+      <c r="E32" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="J32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O32" s="1"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="6">
+        <v>0.24390243902439024</v>
+      </c>
+      <c r="C33" s="1">
         <v>3</v>
       </c>
-      <c r="C33" s="2">
+      <c r="D33" s="2">
         <v>46161</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>2</v>
+      <c r="E33" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="J33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="6">
+        <v>0.6097560975609756</v>
+      </c>
+      <c r="C34" s="1">
         <v>3</v>
       </c>
-      <c r="C34" s="2">
+      <c r="D34" s="2">
         <v>46162</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>2</v>
+      <c r="E34" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="I34" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="J34" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="6">
+        <v>0.69047619047619047</v>
+      </c>
+      <c r="C35" s="1">
         <v>3</v>
       </c>
-      <c r="C35" s="2">
+      <c r="D35" s="2">
         <v>46163</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>2</v>
+      <c r="E35" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="I35" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="J35" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="6">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1">
         <v>3</v>
       </c>
-      <c r="C36" s="2">
+      <c r="D36" s="2">
         <v>46164</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>2</v>
+      <c r="E36" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="J36" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="6">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1">
         <v>3</v>
       </c>
-      <c r="C37" s="2">
+      <c r="D37" s="2">
         <v>46165</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>2</v>
+      <c r="E37" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="1">
-        <v>4</v>
-      </c>
-      <c r="C38" s="2">
+      <c r="B38" s="6">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1">
+        <v>4</v>
+      </c>
+      <c r="D38" s="2">
         <v>46166</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>2</v>
+      <c r="E38" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
-    </row>
-    <row r="39" spans="1:14" ht="29" x14ac:dyDescent="0.3">
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="1:15" ht="29" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="1">
-        <v>4</v>
-      </c>
-      <c r="C39" s="2">
+      <c r="B39" s="8">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1">
+        <v>4</v>
+      </c>
+      <c r="D39" s="2">
         <v>46167</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>4</v>
+      <c r="E39" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="I39" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="J39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="K39" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="2">
+      <c r="B40" s="5">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="2">
         <v>46168</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="1" t="s">
+      <c r="J40" s="1"/>
+      <c r="K40" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="2">
+      <c r="B41" s="5">
+        <v>0</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="2">
         <v>46169</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1" t="s">
+      <c r="J41" s="1"/>
+      <c r="K41" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O41" s="1"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="2">
+      <c r="B42" s="5">
+        <v>0</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="2">
         <v>46170</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1" t="s">
+      <c r="J42" s="1"/>
+      <c r="K42" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O42" s="1"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="2">
+      <c r="B43" s="5">
+        <v>0</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="2">
         <v>46171</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="J43" s="1"/>
+      <c r="K43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O43" s="1"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="2">
+      <c r="B44" s="5">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="2">
         <v>46172</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="1" t="s">
+      <c r="J44" s="1"/>
+      <c r="K44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O44" s="1"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="2">
+      <c r="B45" s="5">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="2">
         <v>46173</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-      <c r="J45" s="1" t="s">
+      <c r="J45" s="1"/>
+      <c r="K45" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O45" s="1"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="7">
+        <v>0.37209302325581395</v>
+      </c>
+      <c r="C46" s="1">
         <v>1</v>
       </c>
-      <c r="C46" s="2">
+      <c r="D46" s="2">
         <v>46174</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>2</v>
+      <c r="E46" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O46" s="1"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="7">
+        <v>0.88372093023255816</v>
+      </c>
+      <c r="C47" s="1">
         <v>1</v>
       </c>
-      <c r="C47" s="2">
+      <c r="D47" s="2">
         <v>46175</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>2</v>
+      <c r="E47" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O47" s="1"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="8">
         <v>1</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2">
         <v>46176</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>2</v>
+      <c r="E48" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O48" s="1"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="7">
+        <v>0</v>
+      </c>
+      <c r="C49" s="1">
         <v>1</v>
       </c>
-      <c r="C49" s="2">
+      <c r="D49" s="2">
         <v>46177</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>2</v>
+      <c r="E49" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="I49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1" t="s">
+      <c r="J49" s="1"/>
+      <c r="K49" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O49" s="1"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="7">
+        <v>0</v>
+      </c>
+      <c r="C50" s="1">
         <v>1</v>
       </c>
-      <c r="C50" s="2">
+      <c r="D50" s="2">
         <v>46178</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>2</v>
+      <c r="E50" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="I50" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1" t="s">
+      <c r="J50" s="1"/>
+      <c r="K50" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O50" s="1"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="7">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1">
         <v>1</v>
       </c>
-      <c r="C51" s="2">
+      <c r="D51" s="2">
         <v>46179</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>4</v>
+      <c r="E51" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="I51" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1" t="s">
+      <c r="J51" s="1"/>
+      <c r="K51" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O51" s="1"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="2">
+      <c r="B52" s="7">
+        <v>0</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="2">
         <v>46180</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="1"/>
+      <c r="F52" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-      <c r="J52" s="1" t="s">
+      <c r="J52" s="1"/>
+      <c r="K52" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O52" s="1"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="7">
+        <v>0</v>
+      </c>
+      <c r="C53" s="1">
         <v>1</v>
       </c>
-      <c r="C53" s="2">
+      <c r="D53" s="2">
         <v>46181</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>2</v>
+      <c r="E53" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="I53" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
+      <c r="J53" s="1"/>
+      <c r="K53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O53" s="1"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="1"/>
-      <c r="C54" s="2">
+      <c r="B54" s="7">
+        <v>0</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="2">
         <v>46182</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F54" s="1"/>
+      <c r="F54" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1" t="s">
+      <c r="J54" s="1"/>
+      <c r="K54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O54" s="1"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="1"/>
-      <c r="C55" s="2">
+      <c r="B55" s="7">
+        <v>0</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="2">
         <v>46183</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
-      <c r="J55" s="1" t="s">
+      <c r="J55" s="1"/>
+      <c r="K55" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O55" s="1"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="2"/>
+      <c r="C56" s="1"/>
       <c r="D56" s="2"/>
-      <c r="E56" s="1"/>
+      <c r="E56" s="2"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
-      <c r="J56" s="3"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA64FAD-11EC-417A-B565-B0AE4C24D26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8619E98F-56D1-4DEC-902A-D133D5C64391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="51">
   <si>
     <t>Task</t>
   </si>
@@ -219,6 +219,18 @@
   </si>
   <si>
     <t>Progress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WOW(onshore)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WOW(offshore)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bad weather</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -272,18 +284,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -302,7 +308,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -313,19 +319,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -630,7 +633,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -669,7 +672,7 @@
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>0.60980000000000001</v>
       </c>
       <c r="C2" s="1">
@@ -706,7 +709,7 @@
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>0.75609756097560976</v>
       </c>
       <c r="C3" s="1">
@@ -745,7 +748,7 @@
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>0.85365853658536583</v>
       </c>
       <c r="C4" s="1">
@@ -784,7 +787,7 @@
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="1">
@@ -821,7 +824,7 @@
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>0.15789473684210525</v>
       </c>
       <c r="C6" s="1">
@@ -858,7 +861,7 @@
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>0</v>
       </c>
       <c r="C7" s="1"/>
@@ -869,7 +872,7 @@
         <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -887,7 +890,7 @@
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>0</v>
       </c>
       <c r="C8" s="1"/>
@@ -898,7 +901,7 @@
         <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -916,7 +919,7 @@
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>0</v>
       </c>
       <c r="C9" s="1"/>
@@ -927,7 +930,7 @@
         <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -945,7 +948,7 @@
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>0.44736842105263158</v>
       </c>
       <c r="C10" s="1">
@@ -982,7 +985,7 @@
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>0.72972972972972971</v>
       </c>
       <c r="C11" s="1">
@@ -1019,7 +1022,7 @@
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>0.89189189189189189</v>
       </c>
       <c r="C12" s="1">
@@ -1054,7 +1057,7 @@
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>0.94594594594594594</v>
       </c>
       <c r="C13" s="1">
@@ -1091,7 +1094,7 @@
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>0</v>
       </c>
       <c r="C14" s="1"/>
@@ -1120,7 +1123,7 @@
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>0</v>
       </c>
       <c r="C15" s="1"/>
@@ -1131,7 +1134,7 @@
         <v>45</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1149,7 +1152,7 @@
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="6">
         <v>0.29729729729729731</v>
       </c>
       <c r="C16" s="1">
@@ -1184,7 +1187,7 @@
       <c r="A17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>0.51351351351351349</v>
       </c>
       <c r="C17" s="1">
@@ -1221,7 +1224,7 @@
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>0</v>
       </c>
       <c r="C18" s="1"/>
@@ -1254,7 +1257,7 @@
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="6">
         <v>1</v>
       </c>
       <c r="C19" s="1">
@@ -1289,7 +1292,7 @@
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="6">
         <v>0.16216216216216217</v>
       </c>
       <c r="C20" s="1">
@@ -1324,7 +1327,7 @@
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>0</v>
       </c>
       <c r="C21" s="1"/>
@@ -1353,7 +1356,7 @@
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>0</v>
       </c>
       <c r="C22" s="1"/>
@@ -1382,7 +1385,7 @@
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>0</v>
       </c>
       <c r="C23" s="1"/>
@@ -1411,7 +1414,7 @@
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>0</v>
       </c>
       <c r="C24" s="1"/>
@@ -1440,7 +1443,7 @@
       <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="6">
         <v>0.3783783783783784</v>
       </c>
       <c r="C25" s="1">
@@ -1477,7 +1480,7 @@
       <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="6">
         <v>0.59459459459459463</v>
       </c>
       <c r="C26" s="1">
@@ -1516,7 +1519,7 @@
       <c r="A27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="6">
         <v>0.67567567567567566</v>
       </c>
       <c r="C27" s="1">
@@ -1553,7 +1556,7 @@
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="6">
         <v>0.67567567567567566</v>
       </c>
       <c r="C28" s="1">
@@ -1566,7 +1569,7 @@
         <v>44</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>9</v>
@@ -1592,7 +1595,7 @@
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="6">
         <v>0.89189189189189189</v>
       </c>
       <c r="C29" s="1">
@@ -1629,7 +1632,7 @@
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>0</v>
       </c>
       <c r="C30" s="1"/>
@@ -1658,7 +1661,7 @@
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="6">
         <v>0.89189189189189189</v>
       </c>
       <c r="C31" s="1">
@@ -1671,7 +1674,7 @@
         <v>44</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -1689,7 +1692,7 @@
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="6">
         <v>1</v>
       </c>
       <c r="C32" s="1">
@@ -1726,7 +1729,7 @@
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>0.24390243902439024</v>
       </c>
       <c r="C33" s="1">
@@ -1763,7 +1766,7 @@
       <c r="A34" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="5">
         <v>0.6097560975609756</v>
       </c>
       <c r="C34" s="1">
@@ -1800,7 +1803,7 @@
       <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="5">
         <v>0.69047619047619047</v>
       </c>
       <c r="C35" s="1">
@@ -1837,7 +1840,7 @@
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="5">
         <v>1</v>
       </c>
       <c r="C36" s="1">
@@ -1874,7 +1877,7 @@
       <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="5">
         <v>1</v>
       </c>
       <c r="C37" s="1">
@@ -1911,7 +1914,7 @@
       <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="5">
         <v>1</v>
       </c>
       <c r="C38" s="1">
@@ -1950,7 +1953,7 @@
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="7">
         <v>0</v>
       </c>
       <c r="C39" s="1">
@@ -1963,7 +1966,7 @@
         <v>44</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>9</v>
@@ -1989,7 +1992,7 @@
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="4">
         <v>0</v>
       </c>
       <c r="C40" s="1"/>
@@ -2018,7 +2021,7 @@
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="4">
         <v>0</v>
       </c>
       <c r="C41" s="1"/>
@@ -2047,7 +2050,7 @@
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="4">
         <v>0</v>
       </c>
       <c r="C42" s="1"/>
@@ -2076,7 +2079,7 @@
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="4">
         <v>0</v>
       </c>
       <c r="C43" s="1"/>
@@ -2105,7 +2108,7 @@
       <c r="A44" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="4">
         <v>0</v>
       </c>
       <c r="C44" s="1"/>
@@ -2116,7 +2119,7 @@
         <v>45</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -2134,7 +2137,7 @@
       <c r="A45" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="4">
         <v>0</v>
       </c>
       <c r="C45" s="1"/>
@@ -2145,7 +2148,7 @@
         <v>45</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -2163,7 +2166,7 @@
       <c r="A46" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="6">
         <v>0.37209302325581395</v>
       </c>
       <c r="C46" s="1">
@@ -2198,7 +2201,7 @@
       <c r="A47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="6">
         <v>0.88372093023255816</v>
       </c>
       <c r="C47" s="1">
@@ -2233,7 +2236,7 @@
       <c r="A48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="7">
         <v>1</v>
       </c>
       <c r="C48" s="1">
@@ -2268,7 +2271,7 @@
       <c r="A49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="6">
         <v>0</v>
       </c>
       <c r="C49" s="1">
@@ -2305,7 +2308,7 @@
       <c r="A50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="6">
         <v>0</v>
       </c>
       <c r="C50" s="1">
@@ -2342,7 +2345,7 @@
       <c r="A51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="6">
         <v>0</v>
       </c>
       <c r="C51" s="1">
@@ -2355,7 +2358,7 @@
         <v>44</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>9</v>
@@ -2368,7 +2371,7 @@
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -2379,7 +2382,7 @@
       <c r="A52" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="6">
         <v>0</v>
       </c>
       <c r="C52" s="1"/>
@@ -2390,7 +2393,7 @@
         <v>45</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -2408,7 +2411,7 @@
       <c r="A53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="6">
         <v>0</v>
       </c>
       <c r="C53" s="1">
@@ -2445,7 +2448,7 @@
       <c r="A54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="6">
         <v>0</v>
       </c>
       <c r="C54" s="1"/>
@@ -2456,7 +2459,7 @@
         <v>45</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -2474,7 +2477,7 @@
       <c r="A55" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="6">
         <v>0</v>
       </c>
       <c r="C55" s="1"/>
@@ -2485,7 +2488,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2500,16 +2503,39 @@
       <c r="O55" s="1"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="3"/>
+      <c r="A56" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="6">
+        <v>0</v>
+      </c>
+      <c r="C56" s="1">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2">
+        <v>46184</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8619E98F-56D1-4DEC-902A-D133D5C64391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7549E2-569C-4767-9638-40565AE69BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="51">
   <si>
     <t>Task</t>
   </si>
@@ -319,16 +319,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1676,10 +1676,18 @@
       <c r="F31" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K31" s="1" t="s">
         <v>33</v>
       </c>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7549E2-569C-4767-9638-40565AE69BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34FF519-75C8-45F0-9297-BC3297A87A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="52">
   <si>
     <t>Task</t>
   </si>
@@ -231,6 +231,10 @@
   </si>
   <si>
     <t>bad weather</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D10 crane issue we change to D11.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2199,7 +2203,9 @@
         <v>10</v>
       </c>
       <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
+      <c r="K46" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34FF519-75C8-45F0-9297-BC3297A87A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1980FEA2-C217-43F2-A380-0C3322818F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="52">
   <si>
     <t>Task</t>
   </si>
@@ -617,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -2551,6 +2551,38 @@
         <v>33</v>
       </c>
     </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="6">
+        <v>0</v>
+      </c>
+      <c r="C57" s="1">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2">
+        <v>46185</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1980FEA2-C217-43F2-A380-0C3322818F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B4422A-94A5-451C-8E3A-2FD26C9F394D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="51">
   <si>
     <t>Task</t>
   </si>
@@ -152,10 +152,6 @@
   </si>
   <si>
     <t>Assistant</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nan</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -617,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -638,7 +634,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>27</v>
@@ -647,10 +643,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>28</v>
@@ -674,7 +670,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="4">
         <v>0.60980000000000001</v>
@@ -686,7 +682,7 @@
         <v>46130</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>2</v>
@@ -711,7 +707,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="5">
         <v>0.75609756097560976</v>
@@ -723,7 +719,7 @@
         <v>46131</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>2</v>
@@ -750,7 +746,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="5">
         <v>0.85365853658536583</v>
@@ -762,7 +758,7 @@
         <v>46132</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>2</v>
@@ -789,7 +785,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
@@ -801,7 +797,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>2</v>
@@ -826,7 +822,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="6">
         <v>0.15789473684210525</v>
@@ -838,7 +834,7 @@
         <v>46134</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>2</v>
@@ -873,15 +869,17 @@
         <v>46135</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="K7" s="1" t="s">
         <v>17</v>
       </c>
@@ -902,15 +900,17 @@
         <v>46136</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="K8" s="1" t="s">
         <v>17</v>
       </c>
@@ -931,15 +931,17 @@
         <v>46137</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="K9" s="1" t="s">
         <v>17</v>
       </c>
@@ -950,7 +952,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="6">
         <v>0.44736842105263158</v>
@@ -962,7 +964,7 @@
         <v>46138</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>2</v>
@@ -987,7 +989,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="6">
         <v>0.72972972972972971</v>
@@ -999,7 +1001,7 @@
         <v>46139</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>2</v>
@@ -1024,7 +1026,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="6">
         <v>0.89189189189189189</v>
@@ -1036,7 +1038,7 @@
         <v>46140</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>2</v>
@@ -1059,7 +1061,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6">
         <v>0.94594594594594594</v>
@@ -1071,7 +1073,7 @@
         <v>46141</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>2</v>
@@ -1106,14 +1108,16 @@
         <v>46142</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
         <v>17</v>
@@ -1135,14 +1139,16 @@
         <v>46143</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1" t="s">
         <v>17</v>
@@ -1154,7 +1160,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6">
         <v>0.29729729729729731</v>
@@ -1166,7 +1172,7 @@
         <v>46144</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>2</v>
@@ -1189,7 +1195,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="6">
         <v>0.51351351351351349</v>
@@ -1201,7 +1207,7 @@
         <v>46145</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>2</v>
@@ -1236,18 +1242,16 @@
         <v>46146</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
         <v>17</v>
@@ -1259,7 +1263,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" s="6">
         <v>1</v>
@@ -1271,7 +1275,7 @@
         <v>46147</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>2</v>
@@ -1294,7 +1298,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="6">
         <v>0.16216216216216217</v>
@@ -1306,7 +1310,7 @@
         <v>46148</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>2</v>
@@ -1339,7 +1343,7 @@
         <v>46149</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -1368,7 +1372,7 @@
         <v>46150</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>6</v>
@@ -1397,7 +1401,7 @@
         <v>46151</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -1426,7 +1430,7 @@
         <v>46152</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -1445,7 +1449,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="6">
         <v>0.3783783783783784</v>
@@ -1457,7 +1461,7 @@
         <v>46153</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>2</v>
@@ -1482,7 +1486,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6">
         <v>0.59459459459459463</v>
@@ -1494,7 +1498,7 @@
         <v>46154</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>2</v>
@@ -1521,7 +1525,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="6">
         <v>0.67567567567567566</v>
@@ -1533,7 +1537,7 @@
         <v>46155</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>2</v>
@@ -1558,7 +1562,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="6">
         <v>0.67567567567567566</v>
@@ -1570,10 +1574,10 @@
         <v>46156</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>9</v>
@@ -1597,7 +1601,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="6">
         <v>0.89189189189189189</v>
@@ -1609,7 +1613,7 @@
         <v>46157</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>2</v>
@@ -1644,7 +1648,7 @@
         <v>46158</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1652,7 +1656,9 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K30" s="1" t="s">
         <v>17</v>
       </c>
@@ -1663,7 +1669,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="6">
         <v>0.89189189189189189</v>
@@ -1675,10 +1681,10 @@
         <v>46159</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>9</v>
@@ -1693,7 +1699,7 @@
         <v>10</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -1702,7 +1708,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="6">
         <v>1</v>
@@ -1714,7 +1720,7 @@
         <v>46160</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>2</v>
@@ -1739,7 +1745,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5">
         <v>0.24390243902439024</v>
@@ -1751,7 +1757,7 @@
         <v>46161</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>2</v>
@@ -1776,7 +1782,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5">
         <v>0.6097560975609756</v>
@@ -1788,7 +1794,7 @@
         <v>46162</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>2</v>
@@ -1813,7 +1819,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5">
         <v>0.69047619047619047</v>
@@ -1825,7 +1831,7 @@
         <v>46163</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>2</v>
@@ -1850,7 +1856,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5">
         <v>1</v>
@@ -1862,7 +1868,7 @@
         <v>46164</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>2</v>
@@ -1887,7 +1893,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5">
         <v>1</v>
@@ -1899,7 +1905,7 @@
         <v>46165</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>2</v>
@@ -1924,7 +1930,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5">
         <v>1</v>
@@ -1936,7 +1942,7 @@
         <v>46166</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>2</v>
@@ -1954,7 +1960,7 @@
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -1963,7 +1969,7 @@
     </row>
     <row r="39" spans="1:15" ht="29" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="7">
         <v>0</v>
@@ -1975,10 +1981,10 @@
         <v>46167</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>9</v>
@@ -2012,7 +2018,7 @@
         <v>46168</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>7</v>
@@ -2020,7 +2026,9 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="J40" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K40" s="1" t="s">
         <v>25</v>
       </c>
@@ -2041,7 +2049,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>7</v>
@@ -2049,7 +2057,9 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K41" s="1" t="s">
         <v>25</v>
       </c>
@@ -2070,7 +2080,7 @@
         <v>46170</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>7</v>
@@ -2078,7 +2088,9 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K42" s="1" t="s">
         <v>25</v>
       </c>
@@ -2099,7 +2111,7 @@
         <v>46171</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2107,7 +2119,9 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+      <c r="J43" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K43" s="1" t="s">
         <v>17</v>
       </c>
@@ -2128,15 +2142,17 @@
         <v>46172</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K44" s="1" t="s">
         <v>17</v>
       </c>
@@ -2157,15 +2173,17 @@
         <v>46173</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
+      <c r="J45" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K45" s="1" t="s">
         <v>17</v>
       </c>
@@ -2176,7 +2194,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="6">
         <v>0.37209302325581395</v>
@@ -2188,7 +2206,7 @@
         <v>46174</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>2</v>
@@ -2204,7 +2222,7 @@
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -2213,7 +2231,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="6">
         <v>0.88372093023255816</v>
@@ -2225,7 +2243,7 @@
         <v>46175</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>2</v>
@@ -2248,7 +2266,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" s="7">
         <v>1</v>
@@ -2260,7 +2278,7 @@
         <v>46176</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>2</v>
@@ -2283,7 +2301,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="6">
         <v>0</v>
@@ -2295,7 +2313,7 @@
         <v>46177</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>2</v>
@@ -2320,7 +2338,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B50" s="6">
         <v>0</v>
@@ -2332,7 +2350,7 @@
         <v>46178</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>2</v>
@@ -2357,7 +2375,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B51" s="6">
         <v>0</v>
@@ -2369,10 +2387,10 @@
         <v>46179</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>9</v>
@@ -2385,7 +2403,7 @@
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -2404,15 +2422,17 @@
         <v>46180</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
+      <c r="J52" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="K52" s="1" t="s">
         <v>17</v>
       </c>
@@ -2423,7 +2443,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B53" s="6">
         <v>0</v>
@@ -2435,7 +2455,7 @@
         <v>46181</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>2</v>
@@ -2470,15 +2490,17 @@
         <v>46182</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K54" s="1" t="s">
         <v>17</v>
       </c>
@@ -2499,15 +2521,17 @@
         <v>46183</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
+      <c r="J55" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K55" s="1" t="s">
         <v>17</v>
       </c>
@@ -2518,7 +2542,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56" s="6">
         <v>0</v>
@@ -2530,10 +2554,10 @@
         <v>46184</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>9</v>
@@ -2548,12 +2572,12 @@
         <v>10</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="6">
         <v>0</v>
@@ -2565,7 +2589,7 @@
         <v>46185</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>2</v>
@@ -2581,6 +2605,52 @@
       </c>
       <c r="K57" s="1" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="6">
+        <v>0</v>
+      </c>
+      <c r="D58" s="2">
+        <v>46186</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="6">
+        <v>0</v>
+      </c>
+      <c r="D59" s="2">
+        <v>46187</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B4422A-94A5-451C-8E3A-2FD26C9F394D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5510E658-8C39-4DB8-B06D-0EB1F1522879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="52">
   <si>
     <t>Task</t>
   </si>
@@ -231,6 +231,10 @@
   </si>
   <si>
     <t>D10 crane issue we change to D11.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -613,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -1975,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="C39" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" s="2">
         <v>46167</v>
@@ -2194,10 +2198,10 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6">
-        <v>0.37209302325581395</v>
+        <v>51</v>
+      </c>
+      <c r="B46" s="4">
+        <v>0</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
@@ -2220,7 +2224,9 @@
       <c r="I46" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J46" s="1"/>
+      <c r="J46" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K46" s="1" t="s">
         <v>50</v>
       </c>
@@ -2234,13 +2240,13 @@
         <v>40</v>
       </c>
       <c r="B47" s="6">
-        <v>0.88372093023255816</v>
+        <v>0.37209302325581395</v>
       </c>
       <c r="C47" s="1">
         <v>1</v>
       </c>
       <c r="D47" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>43</v>
@@ -2258,7 +2264,9 @@
         <v>10</v>
       </c>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
+      <c r="K47" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
@@ -2268,14 +2276,14 @@
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="7">
-        <v>1</v>
+      <c r="B48" s="6">
+        <v>0.88372093023255816</v>
       </c>
       <c r="C48" s="1">
         <v>1</v>
       </c>
       <c r="D48" s="2">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>43</v>
@@ -2301,16 +2309,16 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="6">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="B49" s="7">
+        <v>1</v>
       </c>
       <c r="C49" s="1">
         <v>1</v>
       </c>
       <c r="D49" s="2">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>43</v>
@@ -2325,12 +2333,10 @@
         <v>21</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J49" s="1"/>
-      <c r="K49" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
@@ -2347,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="2">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>43</v>
@@ -2384,13 +2390,13 @@
         <v>1</v>
       </c>
       <c r="D51" s="2">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>9</v>
@@ -2403,7 +2409,7 @@
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -2412,29 +2418,35 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B52" s="6">
         <v>0</v>
       </c>
-      <c r="C52" s="1"/>
+      <c r="C52" s="1">
+        <v>1</v>
+      </c>
       <c r="D52" s="2">
-        <v>46180</v>
+        <v>46179</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -2443,35 +2455,29 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="B53" s="6">
         <v>0</v>
       </c>
-      <c r="C53" s="1">
-        <v>1</v>
-      </c>
+      <c r="C53" s="1"/>
       <c r="D53" s="2">
-        <v>46181</v>
+        <v>46180</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J53" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="K53" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -2480,29 +2486,35 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B54" s="6">
         <v>0</v>
       </c>
-      <c r="C54" s="1"/>
+      <c r="C54" s="1">
+        <v>1</v>
+      </c>
       <c r="D54" s="2">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
@@ -2518,7 +2530,7 @@
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>44</v>
@@ -2542,38 +2554,34 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="B56" s="6">
         <v>0</v>
       </c>
-      <c r="C56" s="1">
-        <v>1</v>
-      </c>
+      <c r="C56" s="1"/>
       <c r="D56" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
       <c r="J56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
@@ -2586,65 +2594,77 @@
         <v>1</v>
       </c>
       <c r="D57" s="2">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="J57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B58" s="6">
         <v>0</v>
       </c>
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
       <c r="D58" s="2">
-        <v>46186</v>
+        <v>46185</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B59" s="6">
         <v>0</v>
       </c>
       <c r="D59" s="2">
-        <v>46187</v>
+        <v>46186</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>10</v>
@@ -2652,6 +2672,62 @@
       <c r="K59" s="1" t="s">
         <v>17</v>
       </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="6">
+        <v>0</v>
+      </c>
+      <c r="D60" s="2">
+        <v>46187</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="6">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2">
+        <v>46188</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="D62" s="2"/>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+      <c r="D63" s="2"/>
+      <c r="F63" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5510E658-8C39-4DB8-B06D-0EB1F1522879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE77183A-0F47-4A15-A2AB-12F145FAC7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="52">
   <si>
     <t>Task</t>
   </si>
@@ -2720,9 +2720,27 @@
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-      <c r="D62" s="2"/>
-      <c r="F62" s="1"/>
+      <c r="A62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="6">
+        <v>0</v>
+      </c>
+      <c r="D62" s="2">
+        <v>46189</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE77183A-0F47-4A15-A2AB-12F145FAC7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820EEB92-CD1E-4711-B693-C082E4BE676E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="52">
   <si>
     <t>Task</t>
   </si>
@@ -1119,10 +1119,9 @@
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1150,10 +1149,9 @@
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="I15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K15" s="1" t="s">
         <v>17</v>
       </c>
@@ -1253,10 +1251,9 @@
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J18" s="1"/>
+      <c r="J18" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="K18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2224,9 +2221,7 @@
       <c r="I46" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
         <v>50</v>
       </c>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820EEB92-CD1E-4711-B693-C082E4BE676E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95083CF-CD17-49D9-8F23-B5041667DCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="54">
   <si>
     <t>Task</t>
   </si>
@@ -235,6 +235,14 @@
   </si>
   <si>
     <t>D10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical issues with crane operation </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2738,9 +2746,27 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-      <c r="D63" s="2"/>
-      <c r="F63" s="1"/>
+      <c r="A63" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B63" s="6">
+        <v>0</v>
+      </c>
+      <c r="D63" s="2">
+        <v>46190</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95083CF-CD17-49D9-8F23-B5041667DCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034A3A03-B0B9-4ABA-BA15-C4E61A8169A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="55">
   <si>
     <t>Task</t>
   </si>
@@ -243,6 +243,10 @@
   </si>
   <si>
     <t xml:space="preserve">Technical issues with crane operation </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paul</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -625,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -2768,6 +2772,52 @@
         <v>53</v>
       </c>
     </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" s="6">
+        <v>0</v>
+      </c>
+      <c r="D64" s="2">
+        <v>46191</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65" s="6">
+        <v>0</v>
+      </c>
+      <c r="D65" s="2">
+        <v>46192</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034A3A03-B0B9-4ABA-BA15-C4E61A8169A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E272F1B-C9DD-4124-9122-CBA9BB67A84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="55">
   <si>
     <t>Task</t>
-  </si>
-  <si>
-    <t>Remark</t>
   </si>
   <si>
     <t>Inspection</t>
@@ -247,6 +244,10 @@
   </si>
   <si>
     <t>Paul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -650,34 +651,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -686,7 +687,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="4">
         <v>0.60980000000000001</v>
@@ -698,22 +699,22 @@
         <v>46130</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -723,7 +724,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="5">
         <v>0.75609756097560976</v>
@@ -735,25 +736,25 @@
         <v>46131</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -762,7 +763,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="5">
         <v>0.85365853658536583</v>
@@ -774,25 +775,25 @@
         <v>46132</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -801,7 +802,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
@@ -813,22 +814,22 @@
         <v>46133</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -838,7 +839,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="6">
         <v>0.15789473684210525</v>
@@ -850,22 +851,22 @@
         <v>46134</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="J6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -875,7 +876,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="4">
         <v>0</v>
@@ -885,19 +886,21 @@
         <v>46135</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -906,7 +909,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
@@ -916,19 +919,21 @@
         <v>46136</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -937,7 +942,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -947,19 +952,21 @@
         <v>46137</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -968,7 +975,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="6">
         <v>0.44736842105263158</v>
@@ -980,22 +987,22 @@
         <v>46138</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="J10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1005,7 +1012,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="6">
         <v>0.72972972972972971</v>
@@ -1017,22 +1024,22 @@
         <v>46139</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="J11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1042,7 +1049,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="6">
         <v>0.89189189189189189</v>
@@ -1054,19 +1061,19 @@
         <v>46140</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1077,7 +1084,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6">
         <v>0.94594594594594594</v>
@@ -1089,23 +1096,23 @@
         <v>46141</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1114,7 +1121,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="4">
         <v>0</v>
@@ -1124,18 +1131,20 @@
         <v>46142</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1144,7 +1153,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" s="4">
         <v>0</v>
@@ -1154,18 +1163,20 @@
         <v>46143</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1174,7 +1185,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="6">
         <v>0.29729729729729731</v>
@@ -1186,19 +1197,19 @@
         <v>46144</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1209,7 +1220,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="6">
         <v>0.51351351351351349</v>
@@ -1221,23 +1232,23 @@
         <v>46145</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -1246,7 +1257,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" s="4">
         <v>0</v>
@@ -1256,18 +1267,20 @@
         <v>46146</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -1276,7 +1289,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="6">
         <v>1</v>
@@ -1288,19 +1301,19 @@
         <v>46147</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1311,7 +1324,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="6">
         <v>0.16216216216216217</v>
@@ -1323,19 +1336,19 @@
         <v>46148</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1346,7 +1359,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" s="4">
         <v>0</v>
@@ -1356,17 +1369,19 @@
         <v>46149</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1375,7 +1390,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -1385,17 +1400,19 @@
         <v>46150</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -1404,7 +1421,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -1414,17 +1431,19 @@
         <v>46151</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -1433,7 +1452,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -1443,17 +1462,19 @@
         <v>46152</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -1462,7 +1483,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="6">
         <v>0.3783783783783784</v>
@@ -1474,22 +1495,22 @@
         <v>46153</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1499,7 +1520,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="6">
         <v>0.59459459459459463</v>
@@ -1511,25 +1532,25 @@
         <v>46154</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -1538,7 +1559,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="6">
         <v>0.67567567567567566</v>
@@ -1550,22 +1571,22 @@
         <v>46155</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1575,7 +1596,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="6">
         <v>0.67567567567567566</v>
@@ -1587,25 +1608,25 @@
         <v>46156</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -1614,7 +1635,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="6">
         <v>0.89189189189189189</v>
@@ -1626,22 +1647,22 @@
         <v>46157</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1651,7 +1672,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" s="4">
         <v>0</v>
@@ -1661,19 +1682,21 @@
         <v>46158</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G30" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -1682,7 +1705,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="6">
         <v>0.89189189189189189</v>
@@ -1694,25 +1717,25 @@
         <v>46159</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -1721,7 +1744,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="6">
         <v>1</v>
@@ -1733,22 +1756,22 @@
         <v>46160</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -1758,7 +1781,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5">
         <v>0.24390243902439024</v>
@@ -1770,22 +1793,22 @@
         <v>46161</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -1795,7 +1818,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5">
         <v>0.6097560975609756</v>
@@ -1807,22 +1830,22 @@
         <v>46162</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -1832,7 +1855,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5">
         <v>0.69047619047619047</v>
@@ -1844,22 +1867,22 @@
         <v>46163</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -1869,7 +1892,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5">
         <v>1</v>
@@ -1881,22 +1904,22 @@
         <v>46164</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -1906,7 +1929,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5">
         <v>1</v>
@@ -1918,22 +1941,22 @@
         <v>46165</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -1943,7 +1966,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="5">
         <v>1</v>
@@ -1955,25 +1978,25 @@
         <v>46166</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -1982,7 +2005,7 @@
     </row>
     <row r="39" spans="1:15" ht="29" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="7">
         <v>0</v>
@@ -1994,25 +2017,25 @@
         <v>46167</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2021,7 +2044,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B40" s="4">
         <v>0</v>
@@ -2031,19 +2054,21 @@
         <v>46168</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G40" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2052,7 +2077,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B41" s="4">
         <v>0</v>
@@ -2062,19 +2087,21 @@
         <v>46169</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -2083,7 +2110,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42" s="4">
         <v>0</v>
@@ -2093,19 +2120,21 @@
         <v>46170</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -2114,7 +2143,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B43" s="4">
         <v>0</v>
@@ -2124,19 +2153,21 @@
         <v>46171</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G43" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -2145,7 +2176,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B44" s="4">
         <v>0</v>
@@ -2155,19 +2186,21 @@
         <v>46172</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G44" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -2176,7 +2209,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B45" s="4">
         <v>0</v>
@@ -2186,19 +2219,21 @@
         <v>46173</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G45" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -2207,7 +2242,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" s="4">
         <v>0</v>
@@ -2219,23 +2254,23 @@
         <v>46174</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -2244,7 +2279,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="6">
         <v>0.37209302325581395</v>
@@ -2256,23 +2291,23 @@
         <v>46174</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -2281,7 +2316,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B48" s="6">
         <v>0.88372093023255816</v>
@@ -2293,19 +2328,19 @@
         <v>46175</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2316,7 +2351,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="7">
         <v>1</v>
@@ -2328,19 +2363,19 @@
         <v>46176</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2351,7 +2386,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" s="6">
         <v>0</v>
@@ -2363,23 +2398,23 @@
         <v>46177</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -2388,7 +2423,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" s="6">
         <v>0</v>
@@ -2400,23 +2435,23 @@
         <v>46178</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -2425,7 +2460,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" s="6">
         <v>0</v>
@@ -2437,23 +2472,23 @@
         <v>46179</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -2462,7 +2497,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53" s="6">
         <v>0</v>
@@ -2472,19 +2507,21 @@
         <v>46180</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G53" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -2493,7 +2530,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" s="6">
         <v>0</v>
@@ -2505,23 +2542,23 @@
         <v>46181</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
@@ -2530,7 +2567,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B55" s="6">
         <v>0</v>
@@ -2540,19 +2577,21 @@
         <v>46182</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G55" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
@@ -2561,7 +2600,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B56" s="6">
         <v>0</v>
@@ -2571,19 +2610,21 @@
         <v>46183</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G56" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
@@ -2592,7 +2633,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" s="6">
         <v>0</v>
@@ -2604,30 +2645,30 @@
         <v>46184</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" s="6">
         <v>0</v>
@@ -2639,27 +2680,27 @@
         <v>46185</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B59" s="6">
         <v>0</v>
@@ -2668,21 +2709,24 @@
         <v>46186</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B60" s="6">
         <v>0</v>
@@ -2691,21 +2735,24 @@
         <v>46187</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B61" s="6">
         <v>0</v>
@@ -2714,21 +2761,24 @@
         <v>46188</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B62" s="6">
         <v>0</v>
@@ -2737,21 +2787,24 @@
         <v>46189</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B63" s="6">
         <v>0</v>
@@ -2760,21 +2813,24 @@
         <v>46190</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B64" s="6">
         <v>0</v>
@@ -2783,21 +2839,24 @@
         <v>46191</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F64" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K64" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B65" s="6">
         <v>0</v>
@@ -2806,16 +2865,19 @@
         <v>46192</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F65" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K65" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E272F1B-C9DD-4124-9122-CBA9BB67A84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BD34C0-1461-4126-9A24-53D65428B045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="55">
   <si>
     <t>Task</t>
   </si>
@@ -630,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -2880,6 +2880,29 @@
         <v>52</v>
       </c>
     </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B66" s="6">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2">
+        <v>46193</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BD34C0-1461-4126-9A24-53D65428B045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E64A8D3-269C-4E1B-B7E6-C63CEB5C80B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,10 +47,6 @@
     <t>Date</t>
   </si>
   <si>
-    <t>WOW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Data Processing</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -248,6 +244,10 @@
   </si>
   <si>
     <t>Remark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-Offshore</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -651,34 +651,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -687,7 +687,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4">
         <v>0.60980000000000001</v>
@@ -699,22 +699,22 @@
         <v>46130</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -724,7 +724,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5">
         <v>0.75609756097560976</v>
@@ -736,25 +736,25 @@
         <v>46131</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -763,7 +763,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="5">
         <v>0.85365853658536583</v>
@@ -775,25 +775,25 @@
         <v>46132</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -802,7 +802,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
@@ -814,22 +814,22 @@
         <v>46133</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -839,7 +839,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="6">
         <v>0.15789473684210525</v>
@@ -851,22 +851,22 @@
         <v>46134</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -876,7 +876,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B7" s="4">
         <v>0</v>
@@ -886,21 +886,21 @@
         <v>46135</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -909,7 +909,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
@@ -919,21 +919,21 @@
         <v>46136</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -942,7 +942,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -952,21 +952,21 @@
         <v>46137</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -975,7 +975,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="6">
         <v>0.44736842105263158</v>
@@ -987,22 +987,22 @@
         <v>46138</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="6">
         <v>0.72972972972972971</v>
@@ -1024,22 +1024,22 @@
         <v>46139</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6">
         <v>0.89189189189189189</v>
@@ -1061,19 +1061,19 @@
         <v>46140</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6">
         <v>0.94594594594594594</v>
@@ -1096,23 +1096,23 @@
         <v>46141</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B14" s="4">
         <v>0</v>
@@ -1131,20 +1131,20 @@
         <v>46142</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B15" s="4">
         <v>0</v>
@@ -1163,20 +1163,20 @@
         <v>46143</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="6">
         <v>0.29729729729729731</v>
@@ -1197,19 +1197,19 @@
         <v>46144</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="6">
         <v>0.51351351351351349</v>
@@ -1232,23 +1232,23 @@
         <v>46145</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B18" s="4">
         <v>0</v>
@@ -1267,20 +1267,20 @@
         <v>46146</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="6">
         <v>1</v>
@@ -1301,19 +1301,19 @@
         <v>46147</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="6">
         <v>0.16216216216216217</v>
@@ -1336,19 +1336,19 @@
         <v>46148</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="B21" s="4">
         <v>0</v>
@@ -1369,19 +1369,19 @@
         <v>46149</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -1400,19 +1400,19 @@
         <v>46150</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -1431,19 +1431,19 @@
         <v>46151</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -1462,19 +1462,19 @@
         <v>46152</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="6">
         <v>0.3783783783783784</v>
@@ -1495,22 +1495,22 @@
         <v>46153</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="6">
         <v>0.59459459459459463</v>
@@ -1532,25 +1532,25 @@
         <v>46154</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="6">
         <v>0.67567567567567566</v>
@@ -1571,22 +1571,22 @@
         <v>46155</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="6">
         <v>0.67567567567567566</v>
@@ -1608,25 +1608,25 @@
         <v>46156</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="6">
         <v>0.89189189189189189</v>
@@ -1647,22 +1647,22 @@
         <v>46157</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1672,7 +1672,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B30" s="4">
         <v>0</v>
@@ -1682,21 +1682,21 @@
         <v>46158</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="6">
         <v>0.89189189189189189</v>
@@ -1717,25 +1717,25 @@
         <v>46159</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -1744,7 +1744,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="6">
         <v>1</v>
@@ -1756,22 +1756,22 @@
         <v>46160</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" s="5">
         <v>0.24390243902439024</v>
@@ -1793,22 +1793,22 @@
         <v>46161</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" s="5">
         <v>0.6097560975609756</v>
@@ -1830,22 +1830,22 @@
         <v>46162</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B35" s="5">
         <v>0.69047619047619047</v>
@@ -1867,22 +1867,22 @@
         <v>46163</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" s="5">
         <v>1</v>
@@ -1904,22 +1904,22 @@
         <v>46164</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="5">
         <v>1</v>
@@ -1941,22 +1941,22 @@
         <v>46165</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -1966,7 +1966,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="5">
         <v>1</v>
@@ -1978,25 +1978,25 @@
         <v>46166</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="39" spans="1:15" ht="29" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="7">
         <v>0</v>
@@ -2017,25 +2017,25 @@
         <v>46167</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="B40" s="4">
         <v>0</v>
@@ -2054,21 +2054,21 @@
         <v>46168</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2077,7 +2077,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="B41" s="4">
         <v>0</v>
@@ -2087,21 +2087,21 @@
         <v>46169</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="B42" s="4">
         <v>0</v>
@@ -2120,21 +2120,21 @@
         <v>46170</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B43" s="4">
         <v>0</v>
@@ -2153,21 +2153,21 @@
         <v>46171</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B44" s="4">
         <v>0</v>
@@ -2186,21 +2186,21 @@
         <v>46172</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B45" s="4">
         <v>0</v>
@@ -2219,21 +2219,21 @@
         <v>46173</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" s="4">
         <v>0</v>
@@ -2254,23 +2254,23 @@
         <v>46174</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -2279,7 +2279,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="6">
         <v>0.37209302325581395</v>
@@ -2291,23 +2291,23 @@
         <v>46174</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" s="6">
         <v>0.88372093023255816</v>
@@ -2328,19 +2328,19 @@
         <v>46175</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" s="7">
         <v>1</v>
@@ -2363,19 +2363,19 @@
         <v>46176</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" s="6">
         <v>0</v>
@@ -2398,23 +2398,23 @@
         <v>46177</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" s="6">
         <v>0</v>
@@ -2435,23 +2435,23 @@
         <v>46178</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="6">
         <v>0</v>
@@ -2472,23 +2472,23 @@
         <v>46179</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B53" s="6">
         <v>0</v>
@@ -2507,21 +2507,21 @@
         <v>46180</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="6">
         <v>0</v>
@@ -2542,23 +2542,23 @@
         <v>46181</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
@@ -2567,7 +2567,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B55" s="6">
         <v>0</v>
@@ -2577,21 +2577,21 @@
         <v>46182</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B56" s="6">
         <v>0</v>
@@ -2610,21 +2610,21 @@
         <v>46183</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B57" s="6">
         <v>0</v>
@@ -2645,30 +2645,30 @@
         <v>46184</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" s="6">
         <v>0</v>
@@ -2680,27 +2680,27 @@
         <v>46185</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B59" s="6">
         <v>0</v>
@@ -2709,24 +2709,24 @@
         <v>46186</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B60" s="6">
         <v>0</v>
@@ -2735,24 +2735,24 @@
         <v>46187</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B61" s="6">
         <v>0</v>
@@ -2761,24 +2761,24 @@
         <v>46188</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B62" s="6">
         <v>0</v>
@@ -2787,24 +2787,24 @@
         <v>46189</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B63" s="6">
         <v>0</v>
@@ -2813,24 +2813,24 @@
         <v>46190</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B64" s="6">
         <v>0</v>
@@ -2839,24 +2839,24 @@
         <v>46191</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F64" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K64" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B65" s="6">
         <v>0</v>
@@ -2865,24 +2865,24 @@
         <v>46192</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F65" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K65" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B66" s="6">
         <v>0</v>
@@ -2891,16 +2891,16 @@
         <v>46193</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F66" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K66" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E64A8D3-269C-4E1B-B7E6-C63CEB5C80B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274F2538-6188-49DE-A09F-E67AB0626196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="58">
   <si>
     <t>Task</t>
   </si>
@@ -239,16 +239,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Paul</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Remark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Non-Offshore</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mobilization</t>
+  </si>
+  <si>
+    <t>Demobilization</t>
+  </si>
+  <si>
+    <t>Demob</t>
+  </si>
+  <si>
+    <t>Standby</t>
   </si>
 </sst>
 </file>
@@ -630,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -678,7 +686,7 @@
         <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -686,23 +694,21 @@
       <c r="O1" s="1"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>31</v>
+      <c r="A2" t="s">
+        <v>54</v>
       </c>
       <c r="B2" s="4">
-        <v>0.60980000000000001</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="2">
-        <v>46130</v>
+        <v>46118</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>1</v>
+      <c r="F2" t="s">
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
@@ -713,9 +719,7 @@
       <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -726,14 +730,14 @@
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="5">
-        <v>0.75609756097560976</v>
+      <c r="B3" s="4">
+        <v>0.60980000000000001</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>46131</v>
+        <v>46130</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>41</v>
@@ -745,17 +749,15 @@
         <v>7</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="J3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -766,13 +768,13 @@
         <v>31</v>
       </c>
       <c r="B4" s="5">
-        <v>0.85365853658536583</v>
+        <v>0.75609756097560976</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>46132</v>
+        <v>46131</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>41</v>
@@ -793,7 +795,7 @@
         <v>8</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -805,13 +807,13 @@
         <v>31</v>
       </c>
       <c r="B5" s="5">
-        <v>1</v>
+        <v>0.85365853658536583</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>46133</v>
+        <v>46132</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>41</v>
@@ -831,7 +833,9 @@
       <c r="J5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -839,16 +843,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0.15789473684210525</v>
+        <v>31</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>41</v>
@@ -860,10 +864,10 @@
         <v>7</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>8</v>
@@ -876,32 +880,36 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
       <c r="D7" s="2">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -909,14 +917,14 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="2">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>42</v>
@@ -942,14 +950,14 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2">
-        <v>46137</v>
+        <v>46136</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>42</v>
@@ -975,36 +983,32 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="6">
-        <v>0.44736842105263158</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B10" s="4">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="2">
-        <v>46138</v>
+        <v>46137</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -1015,13 +1019,13 @@
         <v>32</v>
       </c>
       <c r="B11" s="6">
-        <v>0.72972972972972971</v>
+        <v>0.44736842105263158</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>46139</v>
+        <v>46138</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>41</v>
@@ -1052,13 +1056,13 @@
         <v>32</v>
       </c>
       <c r="B12" s="6">
-        <v>0.89189189189189189</v>
+        <v>0.72972972972972971</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>41</v>
@@ -1073,9 +1077,11 @@
         <v>9</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -1087,13 +1093,13 @@
         <v>32</v>
       </c>
       <c r="B13" s="6">
-        <v>0.94594594594594594</v>
+        <v>0.89189189189189189</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>41</v>
@@ -1111,9 +1117,7 @@
         <v>8</v>
       </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -1121,30 +1125,35 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="B14" s="6">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
       <c r="D14" s="2">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="1"/>
-      <c r="J14" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1153,20 +1162,20 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" s="4">
         <v>0</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="2">
-        <v>46143</v>
+        <v>46142</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>7</v>
@@ -1185,34 +1194,31 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0.29729729729729731</v>
-      </c>
-      <c r="C16" s="1">
-        <v>5</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1"/>
       <c r="D16" s="2">
-        <v>46144</v>
+        <v>46143</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -1223,13 +1229,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="6">
-        <v>0.51351351351351349</v>
+        <v>0.29729729729729731</v>
       </c>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="2">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>41</v>
@@ -1247,9 +1253,7 @@
         <v>8</v>
       </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -1257,30 +1261,35 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="4">
-        <v>0</v>
-      </c>
-      <c r="C18" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0.51351351351351349</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5</v>
+      </c>
       <c r="D18" s="2">
-        <v>46146</v>
+        <v>46145</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="1"/>
-      <c r="J18" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -1289,34 +1298,31 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="6">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1">
-        <v>5</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1"/>
       <c r="D19" s="2">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -1324,16 +1330,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="6">
-        <v>0.16216216216216217</v>
+        <v>1</v>
       </c>
       <c r="C20" s="1">
         <v>5</v>
       </c>
       <c r="D20" s="2">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>41</v>
@@ -1359,30 +1365,34 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="4">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="B21" s="6">
+        <v>0.16216216216216217</v>
+      </c>
+      <c r="C21" s="1">
+        <v>5</v>
+      </c>
       <c r="D21" s="2">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+      <c r="H21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="J21" s="1"/>
-      <c r="K21" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -1390,14 +1400,14 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="2">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>42</v>
@@ -1421,14 +1431,14 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="2">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>42</v>
@@ -1452,14 +1462,14 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="2">
-        <v>46152</v>
+        <v>46151</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>42</v>
@@ -1483,36 +1493,30 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="6">
-        <v>0.3783783783783784</v>
-      </c>
-      <c r="C25" s="1">
+        <v>53</v>
+      </c>
+      <c r="B25" s="4">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="2">
+        <v>46152</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="2">
-        <v>46153</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -1523,13 +1527,13 @@
         <v>35</v>
       </c>
       <c r="B26" s="6">
-        <v>0.59459459459459463</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="C26" s="1">
         <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>41</v>
@@ -1549,9 +1553,7 @@
       <c r="J26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -1562,13 +1564,13 @@
         <v>35</v>
       </c>
       <c r="B27" s="6">
-        <v>0.67567567567567566</v>
+        <v>0.59459459459459463</v>
       </c>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="2">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>41</v>
@@ -1588,7 +1590,9 @@
       <c r="J27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -1605,13 +1609,13 @@
         <v>4</v>
       </c>
       <c r="D28" s="2">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>7</v>
@@ -1625,9 +1629,7 @@
       <c r="J28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -1638,19 +1640,19 @@
         <v>35</v>
       </c>
       <c r="B29" s="6">
-        <v>0.89189189189189189</v>
+        <v>0.67567567567567566</v>
       </c>
       <c r="C29" s="1">
         <v>4</v>
       </c>
       <c r="D29" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>7</v>
@@ -1664,7 +1666,9 @@
       <c r="J29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -1672,32 +1676,36 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="4">
-        <v>0</v>
-      </c>
-      <c r="C30" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="B30" s="6">
+        <v>0.89189189189189189</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4</v>
+      </c>
       <c r="D30" s="2">
-        <v>46158</v>
+        <v>46157</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="H30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="J30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -1705,37 +1713,31 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="6">
-        <v>0.89189189189189189</v>
-      </c>
-      <c r="C31" s="1">
-        <v>4</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B31" s="4">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1"/>
       <c r="D31" s="2">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -1747,19 +1749,19 @@
         <v>35</v>
       </c>
       <c r="B32" s="6">
-        <v>1</v>
+        <v>0.89189189189189189</v>
       </c>
       <c r="C32" s="1">
         <v>4</v>
       </c>
       <c r="D32" s="2">
-        <v>46160</v>
+        <v>46159</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>7</v>
@@ -1773,7 +1775,9 @@
       <c r="J32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="1"/>
+      <c r="K32" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -1781,16 +1785,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="5">
-        <v>0.24390243902439024</v>
+        <v>35</v>
+      </c>
+      <c r="B33" s="6">
+        <v>1</v>
       </c>
       <c r="C33" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" s="2">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>41</v>
@@ -1821,13 +1825,13 @@
         <v>36</v>
       </c>
       <c r="B34" s="5">
-        <v>0.6097560975609756</v>
+        <v>0.24390243902439024</v>
       </c>
       <c r="C34" s="1">
         <v>3</v>
       </c>
       <c r="D34" s="2">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>41</v>
@@ -1858,13 +1862,13 @@
         <v>36</v>
       </c>
       <c r="B35" s="5">
-        <v>0.69047619047619047</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="C35" s="1">
         <v>3</v>
       </c>
       <c r="D35" s="2">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>41</v>
@@ -1882,7 +1886,7 @@
         <v>19</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -1895,13 +1899,13 @@
         <v>36</v>
       </c>
       <c r="B36" s="5">
-        <v>1</v>
+        <v>0.69047619047619047</v>
       </c>
       <c r="C36" s="1">
         <v>3</v>
       </c>
       <c r="D36" s="2">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>41</v>
@@ -1938,7 +1942,7 @@
         <v>3</v>
       </c>
       <c r="D37" s="2">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>41</v>
@@ -1966,16 +1970,16 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" s="5">
         <v>1</v>
       </c>
       <c r="C38" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" s="2">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>41</v>
@@ -1995,32 +1999,30 @@
       <c r="J38" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="7">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="B39" s="5">
+        <v>1</v>
       </c>
       <c r="C39" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" s="2">
-        <v>46167</v>
+        <v>46166</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>7</v>
@@ -2032,43 +2034,49 @@
         <v>19</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" ht="29" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="4">
-        <v>0</v>
-      </c>
-      <c r="C40" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="7">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3</v>
+      </c>
       <c r="D40" s="2">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+      <c r="H40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="J40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>23</v>
+      <c r="K40" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2077,14 +2085,14 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41" s="4">
         <v>0</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="2">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>42</v>
@@ -2110,14 +2118,14 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B42" s="4">
         <v>0</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="2">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>42</v>
@@ -2143,20 +2151,20 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B43" s="4">
         <v>0</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="2">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>7</v>
@@ -2167,7 +2175,7 @@
         <v>8</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -2176,20 +2184,20 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" s="4">
         <v>0</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="2">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>7</v>
@@ -2209,14 +2217,14 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B45" s="4">
         <v>0</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="2">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>42</v>
@@ -2242,35 +2250,31 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B46" s="4">
         <v>0</v>
       </c>
-      <c r="C46" s="1">
-        <v>1</v>
-      </c>
+      <c r="C46" s="1"/>
       <c r="D46" s="2">
-        <v>46174</v>
+        <v>46173</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K46" s="1" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -2279,10 +2283,10 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="6">
-        <v>0.37209302325581395</v>
+        <v>49</v>
+      </c>
+      <c r="B47" s="4">
+        <v>0</v>
       </c>
       <c r="C47" s="1">
         <v>1</v>
@@ -2319,13 +2323,13 @@
         <v>38</v>
       </c>
       <c r="B48" s="6">
-        <v>0.88372093023255816</v>
+        <v>0.37209302325581395</v>
       </c>
       <c r="C48" s="1">
         <v>1</v>
       </c>
       <c r="D48" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>41</v>
@@ -2343,7 +2347,9 @@
         <v>8</v>
       </c>
       <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
+      <c r="K48" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
@@ -2353,14 +2359,14 @@
       <c r="A49" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B49" s="7">
-        <v>1</v>
+      <c r="B49" s="6">
+        <v>0.88372093023255816</v>
       </c>
       <c r="C49" s="1">
         <v>1</v>
       </c>
       <c r="D49" s="2">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>41</v>
@@ -2386,16 +2392,16 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="6">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="B50" s="7">
+        <v>1</v>
       </c>
       <c r="C50" s="1">
         <v>1</v>
       </c>
       <c r="D50" s="2">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>41</v>
@@ -2410,12 +2416,10 @@
         <v>19</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J50" s="1"/>
-      <c r="K50" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
@@ -2432,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="2">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>41</v>
@@ -2469,13 +2473,13 @@
         <v>1</v>
       </c>
       <c r="D52" s="2">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>7</v>
@@ -2488,7 +2492,7 @@
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -2497,31 +2501,35 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B53" s="6">
         <v>0</v>
       </c>
-      <c r="C53" s="1"/>
+      <c r="C53" s="1">
+        <v>1</v>
+      </c>
       <c r="D53" s="2">
-        <v>46180</v>
+        <v>46179</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
+      <c r="H53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -2530,35 +2538,31 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B54" s="6">
         <v>0</v>
       </c>
-      <c r="C54" s="1">
-        <v>1</v>
-      </c>
+      <c r="C54" s="1"/>
       <c r="D54" s="2">
-        <v>46181</v>
+        <v>46180</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="K54" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
@@ -2567,31 +2571,35 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B55" s="6">
         <v>0</v>
       </c>
-      <c r="C55" s="1"/>
+      <c r="C55" s="1">
+        <v>1</v>
+      </c>
       <c r="D55" s="2">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
@@ -2600,14 +2608,14 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56" s="6">
         <v>0</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>42</v>
@@ -2633,38 +2641,36 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B57" s="6">
         <v>0</v>
       </c>
-      <c r="C57" s="1">
-        <v>1</v>
-      </c>
+      <c r="C57" s="1"/>
       <c r="D57" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
       <c r="J57" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
@@ -2677,68 +2683,77 @@
         <v>1</v>
       </c>
       <c r="D58" s="2">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H58" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="J58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B59" s="6">
         <v>0</v>
       </c>
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
       <c r="D59" s="2">
-        <v>46186</v>
+        <v>46185</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="H59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B60" s="6">
         <v>0</v>
       </c>
       <c r="D60" s="2">
-        <v>46187</v>
+        <v>46186</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>9</v>
@@ -2752,19 +2767,19 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" s="6">
         <v>0</v>
       </c>
       <c r="D61" s="2">
-        <v>46188</v>
+        <v>46187</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>9</v>
@@ -2778,13 +2793,13 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B62" s="6">
         <v>0</v>
       </c>
       <c r="D62" s="2">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>42</v>
@@ -2804,19 +2819,19 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B63" s="6">
         <v>0</v>
       </c>
       <c r="D63" s="2">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>9</v>
@@ -2825,18 +2840,18 @@
         <v>8</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B64" s="6">
         <v>0</v>
       </c>
       <c r="D64" s="2">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>42</v>
@@ -2848,7 +2863,7 @@
         <v>9</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>51</v>
@@ -2856,13 +2871,13 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B65" s="6">
         <v>0</v>
       </c>
       <c r="D65" s="2">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>42</v>
@@ -2874,33 +2889,153 @@
         <v>9</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
-        <v>54</v>
+      <c r="A66" t="s">
+        <v>55</v>
       </c>
       <c r="B66" s="6">
         <v>0</v>
       </c>
       <c r="D66" s="2">
+        <v>46192</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F66" t="s">
+        <v>56</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>57</v>
+      </c>
+      <c r="B67" s="6">
+        <v>0</v>
+      </c>
+      <c r="D67" s="2">
         <v>46193</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>51</v>
+      <c r="E67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G67" s="1"/>
+      <c r="K67" s="1"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>57</v>
+      </c>
+      <c r="B68" s="6">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2">
+        <v>46194</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>57</v>
+      </c>
+      <c r="B69" s="6">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2">
+        <v>46195</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B70" s="6">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>57</v>
+      </c>
+      <c r="B71" s="6">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2">
+        <v>46197</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F71" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>57</v>
+      </c>
+      <c r="B72" s="6">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2">
+        <v>46198</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F72" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>57</v>
+      </c>
+      <c r="B73" s="6">
+        <v>0</v>
+      </c>
+      <c r="D73" s="2">
+        <v>46199</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F73" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274F2538-6188-49DE-A09F-E67AB0626196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B335F856-450E-4C75-BE76-4CB4B7CD8828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="59">
   <si>
     <t>Task</t>
   </si>
@@ -250,13 +250,19 @@
     <t>Mobilization</t>
   </si>
   <si>
+    <t>Standby</t>
+  </si>
+  <si>
+    <t>Mobilization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Demobilization</t>
-  </si>
-  <si>
-    <t>Demob</t>
-  </si>
-  <si>
-    <t>Standby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -708,7 +714,7 @@
         <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
@@ -2897,7 +2903,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B66" s="6">
         <v>0</v>
@@ -2909,7 +2915,7 @@
         <v>41</v>
       </c>
       <c r="F66" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>9</v>
@@ -2919,7 +2925,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B67" s="6">
         <v>0</v>
@@ -2931,14 +2937,14 @@
         <v>42</v>
       </c>
       <c r="F67" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G67" s="1"/>
       <c r="K67" s="1"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B68" s="6">
         <v>0</v>
@@ -2950,12 +2956,12 @@
         <v>42</v>
       </c>
       <c r="F68" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B69" s="6">
         <v>0</v>
@@ -2967,12 +2973,12 @@
         <v>42</v>
       </c>
       <c r="F69" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B70" s="6">
         <v>0</v>
@@ -2984,12 +2990,12 @@
         <v>42</v>
       </c>
       <c r="F70" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B71" s="6">
         <v>0</v>
@@ -3001,12 +3007,12 @@
         <v>42</v>
       </c>
       <c r="F71" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B72" s="6">
         <v>0</v>
@@ -3018,12 +3024,12 @@
         <v>42</v>
       </c>
       <c r="F72" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B73" s="6">
         <v>0</v>
@@ -3035,7 +3041,7 @@
         <v>42</v>
       </c>
       <c r="F73" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B335F856-450E-4C75-BE76-4CB4B7CD8828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2188032-FE57-4FB3-BA40-5C6DD50574B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="59">
   <si>
     <t>Task</t>
   </si>
@@ -253,15 +253,15 @@
     <t>Standby</t>
   </si>
   <si>
-    <t>Mobilization</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Demob</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Demobilization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mob</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -315,12 +315,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -339,7 +345,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -360,6 +366,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -644,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -699,38 +718,38 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2">
+      <c r="B2" s="9">
+        <v>0</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="11">
         <v>46118</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="E2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2901,27 +2920,27 @@
         <v>51</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="6">
-        <v>0</v>
-      </c>
-      <c r="D66" s="2">
+    <row r="66" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B66" s="12">
+        <v>0</v>
+      </c>
+      <c r="D66" s="11">
         <v>46192</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F66" t="s">
-        <v>57</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
+      <c r="E66" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
@@ -3041,6 +3060,601 @@
         <v>42</v>
       </c>
       <c r="F73" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>55</v>
+      </c>
+      <c r="B74" s="6">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F74" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>55</v>
+      </c>
+      <c r="B75" s="6">
+        <v>2</v>
+      </c>
+      <c r="D75" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F75" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>55</v>
+      </c>
+      <c r="B76" s="6">
+        <v>3</v>
+      </c>
+      <c r="D76" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F76" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>55</v>
+      </c>
+      <c r="B77" s="6">
+        <v>4</v>
+      </c>
+      <c r="D77" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F77" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>55</v>
+      </c>
+      <c r="B78" s="6">
+        <v>5</v>
+      </c>
+      <c r="D78" s="2">
+        <v>46204</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F78" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>55</v>
+      </c>
+      <c r="B79" s="6">
+        <v>6</v>
+      </c>
+      <c r="D79" s="2">
+        <v>46205</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>55</v>
+      </c>
+      <c r="B80" s="6">
+        <v>7</v>
+      </c>
+      <c r="D80" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F80" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>55</v>
+      </c>
+      <c r="B81" s="6">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>55</v>
+      </c>
+      <c r="B82" s="6">
+        <v>9</v>
+      </c>
+      <c r="D82" s="2">
+        <v>46208</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F82" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>55</v>
+      </c>
+      <c r="B83" s="6">
+        <v>10</v>
+      </c>
+      <c r="D83" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F83" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>55</v>
+      </c>
+      <c r="B84" s="6">
+        <v>11</v>
+      </c>
+      <c r="D84" s="2">
+        <v>46210</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>55</v>
+      </c>
+      <c r="B85" s="6">
+        <v>12</v>
+      </c>
+      <c r="D85" s="2">
+        <v>46211</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F85" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>55</v>
+      </c>
+      <c r="B86" s="6">
+        <v>13</v>
+      </c>
+      <c r="D86" s="2">
+        <v>46212</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F86" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>55</v>
+      </c>
+      <c r="B87" s="6">
+        <v>14</v>
+      </c>
+      <c r="D87" s="2">
+        <v>46213</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F87" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>55</v>
+      </c>
+      <c r="B88" s="6">
+        <v>15</v>
+      </c>
+      <c r="D88" s="2">
+        <v>46214</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F88" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>55</v>
+      </c>
+      <c r="B89" s="6">
+        <v>16</v>
+      </c>
+      <c r="D89" s="2">
+        <v>46215</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F89" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>55</v>
+      </c>
+      <c r="B90" s="6">
+        <v>17</v>
+      </c>
+      <c r="D90" s="2">
+        <v>46216</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F90" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>55</v>
+      </c>
+      <c r="B91" s="6">
+        <v>18</v>
+      </c>
+      <c r="D91" s="2">
+        <v>46217</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F91" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>55</v>
+      </c>
+      <c r="B92" s="6">
+        <v>19</v>
+      </c>
+      <c r="D92" s="2">
+        <v>46218</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>55</v>
+      </c>
+      <c r="B93" s="6">
+        <v>20</v>
+      </c>
+      <c r="D93" s="2">
+        <v>46219</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F93" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>55</v>
+      </c>
+      <c r="B94" s="6">
+        <v>21</v>
+      </c>
+      <c r="D94" s="2">
+        <v>46220</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F94" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>55</v>
+      </c>
+      <c r="B95" s="6">
+        <v>22</v>
+      </c>
+      <c r="D95" s="2">
+        <v>46221</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F95" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>55</v>
+      </c>
+      <c r="B96" s="6">
+        <v>23</v>
+      </c>
+      <c r="D96" s="2">
+        <v>46222</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F96" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>55</v>
+      </c>
+      <c r="B97" s="6">
+        <v>24</v>
+      </c>
+      <c r="D97" s="2">
+        <v>46223</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F97" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>55</v>
+      </c>
+      <c r="B98" s="6">
+        <v>25</v>
+      </c>
+      <c r="D98" s="2">
+        <v>46224</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F98" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>55</v>
+      </c>
+      <c r="B99" s="6">
+        <v>26</v>
+      </c>
+      <c r="D99" s="2">
+        <v>46225</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F99" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>55</v>
+      </c>
+      <c r="B100" s="6">
+        <v>27</v>
+      </c>
+      <c r="D100" s="2">
+        <v>46226</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F100" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>55</v>
+      </c>
+      <c r="B101" s="6">
+        <v>28</v>
+      </c>
+      <c r="D101" s="2">
+        <v>46227</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>55</v>
+      </c>
+      <c r="B102" s="6">
+        <v>29</v>
+      </c>
+      <c r="D102" s="2">
+        <v>46228</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>55</v>
+      </c>
+      <c r="B103" s="6">
+        <v>30</v>
+      </c>
+      <c r="D103" s="2">
+        <v>46229</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F103" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>55</v>
+      </c>
+      <c r="B104" s="6">
+        <v>31</v>
+      </c>
+      <c r="D104" s="2">
+        <v>46230</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>55</v>
+      </c>
+      <c r="B105" s="6">
+        <v>32</v>
+      </c>
+      <c r="D105" s="2">
+        <v>46231</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F105" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>55</v>
+      </c>
+      <c r="B106" s="6">
+        <v>33</v>
+      </c>
+      <c r="D106" s="2">
+        <v>46232</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F106" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>55</v>
+      </c>
+      <c r="B107" s="6">
+        <v>34</v>
+      </c>
+      <c r="D107" s="2">
+        <v>46233</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F107" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>55</v>
+      </c>
+      <c r="B108" s="6">
+        <v>35</v>
+      </c>
+      <c r="D108" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108" t="s">
         <v>55</v>
       </c>
     </row>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2188032-FE57-4FB3-BA40-5C6DD50574B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F11EF1-0DE4-412F-BA8D-9FD6EBF2334B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3068,7 +3068,7 @@
         <v>55</v>
       </c>
       <c r="B74" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="2">
         <v>46200</v>
@@ -3085,7 +3085,7 @@
         <v>55</v>
       </c>
       <c r="B75" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D75" s="2">
         <v>46201</v>
@@ -3102,7 +3102,7 @@
         <v>55</v>
       </c>
       <c r="B76" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D76" s="2">
         <v>46202</v>
@@ -3119,7 +3119,7 @@
         <v>55</v>
       </c>
       <c r="B77" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D77" s="2">
         <v>46203</v>
@@ -3136,7 +3136,7 @@
         <v>55</v>
       </c>
       <c r="B78" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D78" s="2">
         <v>46204</v>
@@ -3153,7 +3153,7 @@
         <v>55</v>
       </c>
       <c r="B79" s="6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D79" s="2">
         <v>46205</v>
@@ -3170,7 +3170,7 @@
         <v>55</v>
       </c>
       <c r="B80" s="6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D80" s="2">
         <v>46206</v>
@@ -3187,7 +3187,7 @@
         <v>55</v>
       </c>
       <c r="B81" s="6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D81" s="2">
         <v>46207</v>
@@ -3204,7 +3204,7 @@
         <v>55</v>
       </c>
       <c r="B82" s="6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D82" s="2">
         <v>46208</v>
@@ -3221,7 +3221,7 @@
         <v>55</v>
       </c>
       <c r="B83" s="6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D83" s="2">
         <v>46209</v>
@@ -3238,7 +3238,7 @@
         <v>55</v>
       </c>
       <c r="B84" s="6">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D84" s="2">
         <v>46210</v>
@@ -3255,7 +3255,7 @@
         <v>55</v>
       </c>
       <c r="B85" s="6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D85" s="2">
         <v>46211</v>
@@ -3272,7 +3272,7 @@
         <v>55</v>
       </c>
       <c r="B86" s="6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D86" s="2">
         <v>46212</v>
@@ -3289,7 +3289,7 @@
         <v>55</v>
       </c>
       <c r="B87" s="6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D87" s="2">
         <v>46213</v>
@@ -3306,7 +3306,7 @@
         <v>55</v>
       </c>
       <c r="B88" s="6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D88" s="2">
         <v>46214</v>
@@ -3323,7 +3323,7 @@
         <v>55</v>
       </c>
       <c r="B89" s="6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D89" s="2">
         <v>46215</v>
@@ -3340,7 +3340,7 @@
         <v>55</v>
       </c>
       <c r="B90" s="6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D90" s="2">
         <v>46216</v>
@@ -3357,7 +3357,7 @@
         <v>55</v>
       </c>
       <c r="B91" s="6">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D91" s="2">
         <v>46217</v>
@@ -3374,7 +3374,7 @@
         <v>55</v>
       </c>
       <c r="B92" s="6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D92" s="2">
         <v>46218</v>
@@ -3391,7 +3391,7 @@
         <v>55</v>
       </c>
       <c r="B93" s="6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D93" s="2">
         <v>46219</v>
@@ -3408,7 +3408,7 @@
         <v>55</v>
       </c>
       <c r="B94" s="6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D94" s="2">
         <v>46220</v>
@@ -3425,7 +3425,7 @@
         <v>55</v>
       </c>
       <c r="B95" s="6">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D95" s="2">
         <v>46221</v>
@@ -3442,7 +3442,7 @@
         <v>55</v>
       </c>
       <c r="B96" s="6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D96" s="2">
         <v>46222</v>
@@ -3459,7 +3459,7 @@
         <v>55</v>
       </c>
       <c r="B97" s="6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D97" s="2">
         <v>46223</v>
@@ -3476,7 +3476,7 @@
         <v>55</v>
       </c>
       <c r="B98" s="6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D98" s="2">
         <v>46224</v>
@@ -3493,7 +3493,7 @@
         <v>55</v>
       </c>
       <c r="B99" s="6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D99" s="2">
         <v>46225</v>
@@ -3510,7 +3510,7 @@
         <v>55</v>
       </c>
       <c r="B100" s="6">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D100" s="2">
         <v>46226</v>
@@ -3527,7 +3527,7 @@
         <v>55</v>
       </c>
       <c r="B101" s="6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D101" s="2">
         <v>46227</v>
@@ -3544,7 +3544,7 @@
         <v>55</v>
       </c>
       <c r="B102" s="6">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D102" s="2">
         <v>46228</v>
@@ -3561,7 +3561,7 @@
         <v>55</v>
       </c>
       <c r="B103" s="6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D103" s="2">
         <v>46229</v>
@@ -3578,7 +3578,7 @@
         <v>55</v>
       </c>
       <c r="B104" s="6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D104" s="2">
         <v>46230</v>
@@ -3595,7 +3595,7 @@
         <v>55</v>
       </c>
       <c r="B105" s="6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D105" s="2">
         <v>46231</v>
@@ -3612,7 +3612,7 @@
         <v>55</v>
       </c>
       <c r="B106" s="6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D106" s="2">
         <v>46232</v>
@@ -3629,7 +3629,7 @@
         <v>55</v>
       </c>
       <c r="B107" s="6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D107" s="2">
         <v>46233</v>
@@ -3646,7 +3646,7 @@
         <v>55</v>
       </c>
       <c r="B108" s="6">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D108" s="2">
         <v>46234</v>
